--- a/data/trans_orig/P1428-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1428-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de artritis en 2007</t>
+          <t>Población con diagnóstico de artritis en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13955</t>
+          <t>14242</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34702</t>
+          <t>34008</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19990</t>
+          <t>19747</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41119</t>
+          <t>40737</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38953</t>
+          <t>38565</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69769</t>
+          <t>66743</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>439074</t>
+          <t>439768</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>459821</t>
+          <t>459534</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265561</t>
+          <t>265943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286690</t>
+          <t>286933</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>710688</t>
+          <t>713714</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>741504</t>
+          <t>741892</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8267</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14695</t>
+          <t>14205</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34965</t>
+          <t>34222</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25589</t>
+          <t>26316</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51078</t>
+          <t>51571</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>342257</t>
+          <t>341612</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>358263</t>
+          <t>358667</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>336900</t>
+          <t>337643</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>357170</t>
+          <t>357660</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>687721</t>
+          <t>687228</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713210</t>
+          <t>712483</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26366</t>
+          <t>27227</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49880</t>
+          <t>48956</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22841</t>
+          <t>23777</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44647</t>
+          <t>44828</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54103</t>
+          <t>55891</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85580</t>
+          <t>88074</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>492509</t>
+          <t>493433</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>516023</t>
+          <t>515162</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>123135</t>
+          <t>122954</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>144941</t>
+          <t>144005</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>624591</t>
+          <t>622097</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>656068</t>
+          <t>654280</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111114</t>
+          <t>110753</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>151934</t>
+          <t>152732</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82977</t>
+          <t>82152</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>119203</t>
+          <t>118412</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>203423</t>
+          <t>203391</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>258946</t>
+          <t>256388</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1086400</t>
+          <t>1085602</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1127220</t>
+          <t>1127581</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>595082</t>
+          <t>595873</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>631308</t>
+          <t>632133</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1693674</t>
+          <t>1696232</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1749197</t>
+          <t>1749229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20529</t>
+          <t>20253</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41305</t>
+          <t>40722</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86405</t>
+          <t>84132</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>120749</t>
+          <t>119446</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108941</t>
+          <t>111736</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>154484</t>
+          <t>153121</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>309250</t>
+          <t>309833</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>330026</t>
+          <t>330302</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>448003</t>
+          <t>449306</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>482347</t>
+          <t>484620</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>764823</t>
+          <t>766186</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>810366</t>
+          <t>807571</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,85%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>780</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>280310</t>
+          <t>283096</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>340745</t>
+          <t>342483</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>282767</t>
+          <t>286126</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>348720</t>
+          <t>352397</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>290949</t>
+          <t>289894</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>297430</t>
+          <t>297421</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>908015</t>
+          <t>906277</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>968450</t>
+          <t>965664</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1198240</t>
+          <t>1194563</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1264193</t>
+          <t>1260834</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,5%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>208367</t>
+          <t>209594</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>268447</t>
+          <t>266177</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>555227</t>
+          <t>555915</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>636544</t>
+          <t>639676</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>784162</t>
+          <t>783807</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>884842</t>
+          <t>886243</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3001743</t>
+          <t>3004013</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3061823</t>
+          <t>3060596</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2741580</t>
+          <t>2738448</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2822897</t>
+          <t>2822209</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5763472</t>
+          <t>5762071</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5864152</t>
+          <t>5864507</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de artritis en 2012</t>
+          <t>Población con diagnóstico de artritis en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27055</t>
+          <t>27808</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9279</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26342</t>
+          <t>26567</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22555</t>
+          <t>22791</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46194</t>
+          <t>47083</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>410156</t>
+          <t>409403</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428729</t>
+          <t>427344</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>288112</t>
+          <t>287887</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>305343</t>
+          <t>305175</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>705471</t>
+          <t>704582</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>729110</t>
+          <t>728874</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9993</t>
+          <t>10148</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26806</t>
+          <t>26993</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24544</t>
+          <t>24845</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>21609</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45173</t>
+          <t>45480</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>391991</t>
+          <t>391804</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>408804</t>
+          <t>408649</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313467</t>
+          <t>313166</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328895</t>
+          <t>328787</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>711635</t>
+          <t>711328</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>734409</t>
+          <t>735199</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33884</t>
+          <t>34151</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61964</t>
+          <t>62285</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27839</t>
+          <t>27233</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50945</t>
+          <t>51724</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66138</t>
+          <t>66196</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103871</t>
+          <t>103644</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>567451</t>
+          <t>567130</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>595531</t>
+          <t>595264</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>209184</t>
+          <t>208405</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>232290</t>
+          <t>232896</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>785673</t>
+          <t>785900</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>823406</t>
+          <t>823348</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50533</t>
+          <t>51593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84432</t>
+          <t>85543</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31973</t>
+          <t>30789</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58226</t>
+          <t>58352</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89597</t>
+          <t>90980</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134554</t>
+          <t>131944</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1074577</t>
+          <t>1073466</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1108476</t>
+          <t>1107416</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>706496</t>
+          <t>706370</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>732749</t>
+          <t>733933</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1789177</t>
+          <t>1791787</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1834134</t>
+          <t>1832751</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18628</t>
+          <t>18126</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>91739</t>
+          <t>94624</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132877</t>
+          <t>132044</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117570</t>
+          <t>118910</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164203</t>
+          <t>164462</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>472484</t>
+          <t>472089</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>491968</t>
+          <t>492470</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>627369</t>
+          <t>628202</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>668507</t>
+          <t>665622</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1106640</t>
+          <t>1106381</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1153273</t>
+          <t>1151933</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11542</t>
+          <t>12586</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>188809</t>
+          <t>190741</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>241765</t>
+          <t>244485</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>192666</t>
+          <t>193100</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>251069</t>
+          <t>247027</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255340</t>
+          <t>254296</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265887</t>
+          <t>265891</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>867586</t>
+          <t>864866</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>920542</t>
+          <t>918610</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1125164</t>
+          <t>1129206</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1183567</t>
+          <t>1183133</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,97%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>151593</t>
+          <t>150772</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>204615</t>
+          <t>207965</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>403151</t>
+          <t>399945</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>481287</t>
+          <t>484304</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>566073</t>
+          <t>571863</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>665664</t>
+          <t>670004</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3217295</t>
+          <t>3213945</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3270317</t>
+          <t>3271138</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3065628</t>
+          <t>3062611</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3143764</t>
+          <t>3146970</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6303161</t>
+          <t>6298821</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6402752</t>
+          <t>6396962</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,79%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de artritis en 2016</t>
+          <t>Población con diagnóstico de artritis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>16028</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9899</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27495</t>
+          <t>27404</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17410</t>
+          <t>16632</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39311</t>
+          <t>37374</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413231</t>
+          <t>413064</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425397</t>
+          <t>425324</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>319560</t>
+          <t>319651</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>337156</t>
+          <t>336806</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>736836</t>
+          <t>738773</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>758737</t>
+          <t>759515</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19498</t>
+          <t>19996</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7934</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24293</t>
+          <t>23195</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15442</t>
+          <t>16380</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37929</t>
+          <t>38669</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>357729</t>
+          <t>357231</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>371449</t>
+          <t>371617</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>347980</t>
+          <t>349078</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>364339</t>
+          <t>364817</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>711571</t>
+          <t>710831</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>734058</t>
+          <t>733120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10187</t>
+          <t>10245</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26214</t>
+          <t>26926</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14753</t>
+          <t>14839</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29041</t>
+          <t>29109</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55703</t>
+          <t>54479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>495700</t>
+          <t>494988</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>511727</t>
+          <t>511669</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151370</t>
+          <t>151284</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>632333</t>
+          <t>633557</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658995</t>
+          <t>658927</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41880</t>
+          <t>41195</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71596</t>
+          <t>71004</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32085</t>
+          <t>32328</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58896</t>
+          <t>59147</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82608</t>
+          <t>80860</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121629</t>
+          <t>122364</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1078042</t>
+          <t>1078634</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1107758</t>
+          <t>1108443</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>766980</t>
+          <t>766729</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>793791</t>
+          <t>793548</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1853885</t>
+          <t>1853150</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1892906</t>
+          <t>1894654</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20582</t>
+          <t>20622</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41457</t>
+          <t>40280</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74490</t>
+          <t>74395</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111223</t>
+          <t>111060</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102010</t>
+          <t>101649</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>143203</t>
+          <t>141872</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>579249</t>
+          <t>580426</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>600124</t>
+          <t>600084</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>627021</t>
+          <t>627184</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>663754</t>
+          <t>663849</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1215747</t>
+          <t>1217078</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1256940</t>
+          <t>1257301</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>116319</t>
+          <t>117522</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>163166</t>
+          <t>167041</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116698</t>
+          <t>115974</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>164299</t>
+          <t>163348</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>918859</t>
+          <t>914984</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>965706</t>
+          <t>964503</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1204871</t>
+          <t>1205822</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1252472</t>
+          <t>1253196</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>101642</t>
+          <t>99298</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>144270</t>
+          <t>146003</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>294673</t>
+          <t>298212</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>367234</t>
+          <t>373024</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>415409</t>
+          <t>410771</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>497615</t>
+          <t>498185</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3241452</t>
+          <t>3239719</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3284080</t>
+          <t>3286424</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3164362</t>
+          <t>3158572</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3236923</t>
+          <t>3233384</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6419703</t>
+          <t>6419133</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6501909</t>
+          <t>6506547</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de artritis en 2023</t>
+          <t>Población con diagnóstico de artritis en 2023 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>14236</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31088</t>
+          <t>29730</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26051</t>
+          <t>26391</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44819</t>
+          <t>45173</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44699</t>
+          <t>44361</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69309</t>
+          <t>69655</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>473146</t>
+          <t>474504</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>490351</t>
+          <t>489998</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>401347</t>
+          <t>400993</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>420115</t>
+          <t>419775</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>881091</t>
+          <t>880745</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>905701</t>
+          <t>906039</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12939</t>
+          <t>12967</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28758</t>
+          <t>28074</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29103</t>
+          <t>29327</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47335</t>
+          <t>48166</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47374</t>
+          <t>46944</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72251</t>
+          <t>72115</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>423455</t>
+          <t>424139</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>439274</t>
+          <t>439246</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>332526</t>
+          <t>331695</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>350758</t>
+          <t>350534</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>759822</t>
+          <t>759958</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>784699</t>
+          <t>785129</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9089</t>
+          <t>7471</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45562</t>
+          <t>46726</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>19609</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36866</t>
+          <t>35514</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17565</t>
+          <t>17836</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78793</t>
+          <t>78964</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>620907</t>
+          <t>619743</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>657380</t>
+          <t>658998</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130045</t>
+          <t>131397</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147421</t>
+          <t>147302</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>754587</t>
+          <t>754416</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>815815</t>
+          <t>815544</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55341</t>
+          <t>55930</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83121</t>
+          <t>83082</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102683</t>
+          <t>101377</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>645633</t>
+          <t>602721</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>165773</t>
+          <t>162510</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>962456</t>
+          <t>846404</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>949780</t>
+          <t>949819</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>977560</t>
+          <t>976971</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>327921</t>
+          <t>370833</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>870871</t>
+          <t>872177</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1043999</t>
+          <t>1160051</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1840682</t>
+          <t>1843945</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,9%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23766</t>
+          <t>23919</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45339</t>
+          <t>43981</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110126</t>
+          <t>114463</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>175072</t>
+          <t>176662</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>148096</t>
+          <t>145990</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>207894</t>
+          <t>209086</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>426515</t>
+          <t>427873</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>448088</t>
+          <t>447935</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>661188</t>
+          <t>659598</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>726134</t>
+          <t>721797</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1100220</t>
+          <t>1099028</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1160018</t>
+          <t>1162124</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,84%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>133273</t>
+          <t>132730</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>168886</t>
+          <t>166654</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>131214</t>
+          <t>130402</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169238</t>
+          <t>169905</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236720</t>
+          <t>237122</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>590118</t>
+          <t>592350</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>625731</t>
+          <t>626274</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>830273</t>
+          <t>829606</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>868297</t>
+          <t>869109</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>128557</t>
+          <t>129005</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>195164</t>
+          <t>195690</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>497866</t>
+          <t>499926</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1251380</t>
+          <t>1243666</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>654761</t>
+          <t>635001</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1692826</t>
+          <t>1458652</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3173014</t>
+          <t>3172488</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3239621</t>
+          <t>3239173</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2310374</t>
+          <t>2318088</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3063888</t>
+          <t>3061828</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5237106</t>
+          <t>5471280</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6275171</t>
+          <t>6294931</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1428-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1428-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14242</t>
+          <t>13742</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34008</t>
+          <t>32553</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19747</t>
+          <t>20190</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40737</t>
+          <t>40041</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38565</t>
+          <t>38662</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66743</t>
+          <t>67387</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>439768</t>
+          <t>441223</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>459534</t>
+          <t>460034</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265943</t>
+          <t>266639</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286933</t>
+          <t>286490</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>713714</t>
+          <t>713070</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>741892</t>
+          <t>741795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8267</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25322</t>
+          <t>24432</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14205</t>
+          <t>15265</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34222</t>
+          <t>35747</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26316</t>
+          <t>26371</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51571</t>
+          <t>51837</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>341612</t>
+          <t>342502</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>358667</t>
+          <t>358838</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>337643</t>
+          <t>336118</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>357660</t>
+          <t>356600</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>687228</t>
+          <t>686962</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>712483</t>
+          <t>712428</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27227</t>
+          <t>26920</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48956</t>
+          <t>50401</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23777</t>
+          <t>23647</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44828</t>
+          <t>44491</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55891</t>
+          <t>55839</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88074</t>
+          <t>87630</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>493433</t>
+          <t>491988</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515162</t>
+          <t>515469</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122954</t>
+          <t>123291</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>144005</t>
+          <t>144135</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>622097</t>
+          <t>622541</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>654280</t>
+          <t>654332</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,14%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110753</t>
+          <t>111812</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>152732</t>
+          <t>152136</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82152</t>
+          <t>81315</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118412</t>
+          <t>117655</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>203391</t>
+          <t>205122</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>256388</t>
+          <t>258637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1085602</t>
+          <t>1086198</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1127581</t>
+          <t>1126522</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>595873</t>
+          <t>596630</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>632133</t>
+          <t>632970</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1696232</t>
+          <t>1693983</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1749229</t>
+          <t>1747498</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,5%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20253</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40722</t>
+          <t>39492</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84132</t>
+          <t>84957</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119446</t>
+          <t>121556</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>111736</t>
+          <t>110832</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>153121</t>
+          <t>154129</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>309833</t>
+          <t>311063</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>330302</t>
+          <t>330275</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>449306</t>
+          <t>447196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>484620</t>
+          <t>483795</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>766186</t>
+          <t>765178</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>807571</t>
+          <t>808475</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,94%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>783</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>283096</t>
+          <t>279162</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>342483</t>
+          <t>340712</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>286126</t>
+          <t>282614</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>352397</t>
+          <t>345481</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>289894</t>
+          <t>290761</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>297421</t>
+          <t>297418</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>906277</t>
+          <t>908048</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>965664</t>
+          <t>969598</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1194563</t>
+          <t>1201479</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1260834</t>
+          <t>1264346</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>209594</t>
+          <t>207037</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>266177</t>
+          <t>264711</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>555915</t>
+          <t>551489</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>639676</t>
+          <t>644726</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>783807</t>
+          <t>770612</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>886243</t>
+          <t>887124</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3004013</t>
+          <t>3005479</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3060596</t>
+          <t>3063153</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2738448</t>
+          <t>2733398</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2822209</t>
+          <t>2826635</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5762071</t>
+          <t>5761190</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5864507</t>
+          <t>5877702</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,41%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9867</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27808</t>
+          <t>26247</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9279</t>
+          <t>9072</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26567</t>
+          <t>25573</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22791</t>
+          <t>21001</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47083</t>
+          <t>45424</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>409403</t>
+          <t>410964</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427344</t>
+          <t>428034</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287887</t>
+          <t>288881</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>305175</t>
+          <t>305382</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>704582</t>
+          <t>706241</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>728874</t>
+          <t>730664</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26993</t>
+          <t>26910</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9224</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24845</t>
+          <t>23743</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21609</t>
+          <t>21806</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45480</t>
+          <t>45257</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>391804</t>
+          <t>391887</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>408649</t>
+          <t>409329</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313166</t>
+          <t>314268</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328787</t>
+          <t>329703</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>711328</t>
+          <t>711551</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>735199</t>
+          <t>735002</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34151</t>
+          <t>32735</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62285</t>
+          <t>60627</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27233</t>
+          <t>26731</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51724</t>
+          <t>51294</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66196</t>
+          <t>67631</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103644</t>
+          <t>103920</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>567130</t>
+          <t>568788</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>595264</t>
+          <t>596680</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>208405</t>
+          <t>208835</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>232896</t>
+          <t>233398</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>785900</t>
+          <t>785624</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>823348</t>
+          <t>821913</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51593</t>
+          <t>51226</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85543</t>
+          <t>83465</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30789</t>
+          <t>31968</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58352</t>
+          <t>58684</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90980</t>
+          <t>91642</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131944</t>
+          <t>135506</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1073466</t>
+          <t>1075544</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1107416</t>
+          <t>1107783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>706370</t>
+          <t>706038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>733933</t>
+          <t>732754</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1791787</t>
+          <t>1788225</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1832751</t>
+          <t>1832089</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18126</t>
+          <t>18208</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>39136</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>94624</t>
+          <t>93762</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132044</t>
+          <t>132973</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>118910</t>
+          <t>118912</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164462</t>
+          <t>163341</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>472089</t>
+          <t>471460</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>492470</t>
+          <t>492388</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>628202</t>
+          <t>627273</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>665622</t>
+          <t>666484</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1106381</t>
+          <t>1107502</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1151933</t>
+          <t>1151931</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>994</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12586</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>190741</t>
+          <t>190385</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>244485</t>
+          <t>246308</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>193100</t>
+          <t>192841</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>247027</t>
+          <t>249692</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254296</t>
+          <t>256290</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265891</t>
+          <t>265888</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>864866</t>
+          <t>863043</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>918610</t>
+          <t>918966</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1129206</t>
+          <t>1126541</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1183133</t>
+          <t>1183392</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,99%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>150772</t>
+          <t>148189</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>207965</t>
+          <t>205319</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>399945</t>
+          <t>401626</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>484304</t>
+          <t>482135</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>571863</t>
+          <t>567465</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>670004</t>
+          <t>669785</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3213945</t>
+          <t>3216591</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3271138</t>
+          <t>3273721</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3062611</t>
+          <t>3064780</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3146970</t>
+          <t>3145289</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6298821</t>
+          <t>6299040</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6396962</t>
+          <t>6401360</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16028</t>
+          <t>16571</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10278</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27404</t>
+          <t>28039</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16632</t>
+          <t>16470</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37374</t>
+          <t>38232</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413064</t>
+          <t>412521</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425324</t>
+          <t>425568</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>319651</t>
+          <t>319016</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>336806</t>
+          <t>336777</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>738773</t>
+          <t>737915</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>759515</t>
+          <t>759677</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19996</t>
+          <t>20097</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23195</t>
+          <t>24532</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16380</t>
+          <t>15686</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38669</t>
+          <t>38082</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>357231</t>
+          <t>357130</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>371617</t>
+          <t>371594</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>349078</t>
+          <t>347741</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>364817</t>
+          <t>364449</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>710831</t>
+          <t>711418</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>733120</t>
+          <t>733814</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10245</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26926</t>
+          <t>26119</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>14658</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>35307</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29109</t>
+          <t>28291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>54552</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>494988</t>
+          <t>495795</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>511669</t>
+          <t>511665</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131307</t>
+          <t>130816</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151284</t>
+          <t>151465</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>633557</t>
+          <t>633484</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658927</t>
+          <t>659745</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41195</t>
+          <t>42062</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71004</t>
+          <t>71058</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32328</t>
+          <t>31992</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59147</t>
+          <t>59381</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80860</t>
+          <t>80903</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122364</t>
+          <t>120715</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1078634</t>
+          <t>1078580</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1108443</t>
+          <t>1107576</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>766729</t>
+          <t>766495</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>793548</t>
+          <t>793884</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1853150</t>
+          <t>1854799</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1894654</t>
+          <t>1894611</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20622</t>
+          <t>19906</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40280</t>
+          <t>40459</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74395</t>
+          <t>74206</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111060</t>
+          <t>111679</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101649</t>
+          <t>100432</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141872</t>
+          <t>142903</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>580426</t>
+          <t>580247</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>600084</t>
+          <t>600800</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>627184</t>
+          <t>626565</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>663849</t>
+          <t>664038</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1217078</t>
+          <t>1216047</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1257301</t>
+          <t>1258518</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>117522</t>
+          <t>118361</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>167041</t>
+          <t>163363</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115974</t>
+          <t>118672</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>163348</t>
+          <t>168220</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>914984</t>
+          <t>918662</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>964503</t>
+          <t>963664</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1205822</t>
+          <t>1200950</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1253196</t>
+          <t>1250498</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>99298</t>
+          <t>101148</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>146003</t>
+          <t>145883</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>298212</t>
+          <t>297505</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>373024</t>
+          <t>367109</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>410771</t>
+          <t>410682</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>498185</t>
+          <t>497782</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3239719</t>
+          <t>3239839</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3286424</t>
+          <t>3284574</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3158572</t>
+          <t>3164487</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3233384</t>
+          <t>3234091</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6419133</t>
+          <t>6419536</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6506547</t>
+          <t>6506636</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20725</t>
+          <t>21984</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14236</t>
+          <t>14682</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29730</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>34489</t>
+          <t>38291</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26391</t>
+          <t>29461</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45173</t>
+          <t>49572</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,17 +8703,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>55215</t>
+          <t>60275</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44361</t>
+          <t>48212</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69655</t>
+          <t>75030</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>483509</t>
+          <t>527684</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>474504</t>
+          <t>518002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>489998</t>
+          <t>534986</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>411677</t>
+          <t>448730</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>400993</t>
+          <t>437449</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>419775</t>
+          <t>457560</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,17 +8816,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>895185</t>
+          <t>976415</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>880745</t>
+          <t>961660</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>906039</t>
+          <t>988478</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>504234</t>
+          <t>549668</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>504234</t>
+          <t>549668</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>504234</t>
+          <t>549668</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446166</t>
+          <t>487021</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446166</t>
+          <t>487021</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446166</t>
+          <t>487021</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>950400</t>
+          <t>1036690</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>950400</t>
+          <t>1036690</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>950400</t>
+          <t>1036690</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19708</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12967</t>
+          <t>12855</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28074</t>
+          <t>29418</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38210</t>
+          <t>42855</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29327</t>
+          <t>33280</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48166</t>
+          <t>53853</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>57918</t>
+          <t>63005</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46944</t>
+          <t>51482</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72115</t>
+          <t>76890</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>432505</t>
+          <t>463062</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>424139</t>
+          <t>453794</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>439246</t>
+          <t>470357</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>341651</t>
+          <t>377604</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>331695</t>
+          <t>366606</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>350534</t>
+          <t>387179</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>774155</t>
+          <t>840666</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>759958</t>
+          <t>826781</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>785129</t>
+          <t>852189</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>379861</t>
+          <t>420459</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>379861</t>
+          <t>420459</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>379861</t>
+          <t>420459</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>832073</t>
+          <t>903671</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>832073</t>
+          <t>903671</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>832073</t>
+          <t>903671</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26091</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>18724</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46726</t>
+          <t>36808</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26240</t>
+          <t>29699</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19609</t>
+          <t>22145</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35514</t>
+          <t>41144</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>52330</t>
+          <t>56752</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17836</t>
+          <t>44739</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78964</t>
+          <t>72720</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>640378</t>
+          <t>442592</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>619743</t>
+          <t>432837</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>658998</t>
+          <t>450921</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>140671</t>
+          <t>157798</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131397</t>
+          <t>146353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147302</t>
+          <t>165352</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>781050</t>
+          <t>600391</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>754416</t>
+          <t>584423</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>815544</t>
+          <t>612404</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>666469</t>
+          <t>469645</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>666469</t>
+          <t>469645</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>666469</t>
+          <t>469645</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>833380</t>
+          <t>657143</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>833380</t>
+          <t>657143</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>833380</t>
+          <t>657143</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68610</t>
+          <t>75217</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55930</t>
+          <t>62347</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83082</t>
+          <t>91350</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>288960</t>
+          <t>93535</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>101377</t>
+          <t>79309</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>602721</t>
+          <t>107631</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>357570</t>
+          <t>168753</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>162510</t>
+          <t>145739</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>846404</t>
+          <t>189587</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>964291</t>
+          <t>1054612</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>949819</t>
+          <t>1038479</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>976971</t>
+          <t>1067482</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>684594</t>
+          <t>762040</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>370833</t>
+          <t>747944</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>872177</t>
+          <t>776266</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1648885</t>
+          <t>1816651</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1160051</t>
+          <t>1795817</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1843945</t>
+          <t>1839665</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1032901</t>
+          <t>1129829</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1032901</t>
+          <t>1129829</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1032901</t>
+          <t>1129829</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>973554</t>
+          <t>855575</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>973554</t>
+          <t>855575</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>973554</t>
+          <t>855575</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2006455</t>
+          <t>1985404</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2006455</t>
+          <t>1985404</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2006455</t>
+          <t>1985404</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>32821</t>
+          <t>34560</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23919</t>
+          <t>24798</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43981</t>
+          <t>46355</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>148872</t>
+          <t>155205</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>114463</t>
+          <t>139648</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>176662</t>
+          <t>173969</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>181694</t>
+          <t>189765</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>145990</t>
+          <t>169118</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>209086</t>
+          <t>209263</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>439033</t>
+          <t>529962</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>427873</t>
+          <t>518167</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>447935</t>
+          <t>539724</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>687388</t>
+          <t>672050</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>659598</t>
+          <t>653286</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>721797</t>
+          <t>687607</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1126420</t>
+          <t>1202012</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1099028</t>
+          <t>1182514</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1162124</t>
+          <t>1222659</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>87,85%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>471854</t>
+          <t>564522</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>471854</t>
+          <t>564522</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>471854</t>
+          <t>564522</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>836260</t>
+          <t>827255</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>836260</t>
+          <t>827255</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>836260</t>
+          <t>827255</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1308114</t>
+          <t>1391777</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1308114</t>
+          <t>1391777</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1308114</t>
+          <t>1391777</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>149361</t>
+          <t>162137</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>132730</t>
+          <t>143491</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>166654</t>
+          <t>183501</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,27 +10418,27 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>150383</t>
+          <t>163171</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>130402</t>
+          <t>143864</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169905</t>
+          <t>183381</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -10461,27 +10461,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>239485</t>
+          <t>236194</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>237122</t>
+          <t>233221</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>609643</t>
+          <t>679581</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>592350</t>
+          <t>658217</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>626274</t>
+          <t>698227</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,22 +10531,22 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>849128</t>
+          <t>915775</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>829606</t>
+          <t>895565</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>869109</t>
+          <t>935082</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,67%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>759004</t>
+          <t>841718</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>759004</t>
+          <t>841718</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>759004</t>
+          <t>841718</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>999511</t>
+          <t>1078946</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>999511</t>
+          <t>1078946</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>999511</t>
+          <t>1078946</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>168978</t>
+          <t>179998</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>129005</t>
+          <t>158407</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>195690</t>
+          <t>206738</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>686132</t>
+          <t>521723</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>499926</t>
+          <t>486593</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1243666</t>
+          <t>554878</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>855110</t>
+          <t>701721</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>635001</t>
+          <t>663227</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1458652</t>
+          <t>743753</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3199200</t>
+          <t>3254106</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3172488</t>
+          <t>3227366</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3239173</t>
+          <t>3275697</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2875622</t>
+          <t>3097803</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2318088</t>
+          <t>3064648</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3061828</t>
+          <t>3132933</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6074822</t>
+          <t>6351909</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5471280</t>
+          <t>6309877</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6294931</t>
+          <t>6390403</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3368178</t>
+          <t>3434104</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3368178</t>
+          <t>3434104</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3368178</t>
+          <t>3434104</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3561754</t>
+          <t>3619526</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3561754</t>
+          <t>3619526</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3561754</t>
+          <t>3619526</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6929932</t>
+          <t>7053630</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6929932</t>
+          <t>7053630</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6929932</t>
+          <t>7053630</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
